--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/7.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/7.xlsx
@@ -426,13 +426,13 @@
         <v>-11.15331391415257</v>
       </c>
       <c r="E2">
-        <v>-11.98331792291502</v>
+        <v>-15.49554802157605</v>
       </c>
       <c r="F2">
-        <v>-1.605495458778953</v>
+        <v>-2.235970030886671</v>
       </c>
       <c r="G2">
-        <v>-5.652165071322356</v>
+        <v>-8.454048599030065</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-11.75348971352529</v>
       </c>
       <c r="E3">
-        <v>-13.09423410952869</v>
+        <v>-17.57880003322068</v>
       </c>
       <c r="F3">
-        <v>-1.75083666143714</v>
+        <v>-1.764532059707624</v>
       </c>
       <c r="G3">
-        <v>-5.482483059707012</v>
+        <v>-8.743201578066628</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-12.3173348124178</v>
       </c>
       <c r="E4">
-        <v>-13.75997413034433</v>
+        <v>-17.75416971764172</v>
       </c>
       <c r="F4">
-        <v>-1.440729040525117</v>
+        <v>-1.705568867976355</v>
       </c>
       <c r="G4">
-        <v>-6.36352847570987</v>
+        <v>-7.819728210432469</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-12.76264268094862</v>
       </c>
       <c r="E5">
-        <v>-14.60921697489878</v>
+        <v>-18.48153321275374</v>
       </c>
       <c r="F5">
-        <v>-1.100492868805873</v>
+        <v>-1.32723525103496</v>
       </c>
       <c r="G5">
-        <v>-6.15189854156642</v>
+        <v>-8.079718593813594</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-13.08871462020108</v>
       </c>
       <c r="E6">
-        <v>-14.61876299810695</v>
+        <v>-19.60393813792487</v>
       </c>
       <c r="F6">
-        <v>-1.203059663885703</v>
+        <v>-1.694182958024876</v>
       </c>
       <c r="G6">
-        <v>-6.632271941496827</v>
+        <v>-8.228259461615153</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-13.27118643318396</v>
       </c>
       <c r="E7">
-        <v>-15.22384863806385</v>
+        <v>-19.55249014472373</v>
       </c>
       <c r="F7">
-        <v>-0.9063169226504468</v>
+        <v>-1.409404327188254</v>
       </c>
       <c r="G7">
-        <v>-5.763055104705784</v>
+        <v>-7.696417010185696</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-13.30972766265187</v>
       </c>
       <c r="E8">
-        <v>-16.58639401138774</v>
+        <v>-20.08256161274357</v>
       </c>
       <c r="F8">
-        <v>-1.112226693066528</v>
+        <v>-1.245880460038617</v>
       </c>
       <c r="G8">
-        <v>-5.430504184194914</v>
+        <v>-7.492235803505607</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-13.19066469184141</v>
       </c>
       <c r="E9">
-        <v>-17.25875013272858</v>
+        <v>-19.7767039497915</v>
       </c>
       <c r="F9">
-        <v>-0.8928849452140528</v>
+        <v>-1.753374779159318</v>
       </c>
       <c r="G9">
-        <v>-5.554090159721447</v>
+        <v>-7.030990735701109</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-12.90708992890979</v>
       </c>
       <c r="E10">
-        <v>-17.37002832451906</v>
+        <v>-20.43934649438589</v>
       </c>
       <c r="F10">
-        <v>-0.690880927102171</v>
+        <v>-1.712960390311535</v>
       </c>
       <c r="G10">
-        <v>-5.190731302422121</v>
+        <v>-7.830497415071719</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-12.46108243149386</v>
       </c>
       <c r="E11">
-        <v>-18.32452196195979</v>
+        <v>-22.58023692320014</v>
       </c>
       <c r="F11">
-        <v>-0.3848472170771161</v>
+        <v>-1.073169998391934</v>
       </c>
       <c r="G11">
-        <v>-4.769795437103789</v>
+        <v>-6.643183499594264</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-11.8522054086538</v>
       </c>
       <c r="E12">
-        <v>-20.23404812524815</v>
+        <v>-23.31267230920075</v>
       </c>
       <c r="F12">
-        <v>-0.4020482661962478</v>
+        <v>-1.003085974278082</v>
       </c>
       <c r="G12">
-        <v>-4.499251034543469</v>
+        <v>-6.322954429580562</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-11.07912158183037</v>
       </c>
       <c r="E13">
-        <v>-20.29111142621881</v>
+        <v>-22.05631965135673</v>
       </c>
       <c r="F13">
-        <v>-0.5276088836429856</v>
+        <v>-1.075795094691406</v>
       </c>
       <c r="G13">
-        <v>-4.091643425566243</v>
+        <v>-5.891500961083967</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-10.16373809703577</v>
       </c>
       <c r="E14">
-        <v>-21.00306905275673</v>
+        <v>-23.77805452602102</v>
       </c>
       <c r="F14">
-        <v>-0.1983974536876005</v>
+        <v>-1.06449284984761</v>
       </c>
       <c r="G14">
-        <v>-3.382316006685381</v>
+        <v>-5.888120894088371</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-9.12388686685493</v>
       </c>
       <c r="E15">
-        <v>-22.52397969060285</v>
+        <v>-24.35742296208835</v>
       </c>
       <c r="F15">
-        <v>-0.3763009505824336</v>
+        <v>-0.9171312590939944</v>
       </c>
       <c r="G15">
-        <v>-3.140493897223778</v>
+        <v>-4.365630795487405</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-7.978331310386316</v>
       </c>
       <c r="E16">
-        <v>-22.82635042856901</v>
+        <v>-26.73050183869789</v>
       </c>
       <c r="F16">
-        <v>0.3060948619653543</v>
+        <v>-0.393714061756682</v>
       </c>
       <c r="G16">
-        <v>-2.687372908172652</v>
+        <v>-4.41866573502653</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-6.770427758722818</v>
       </c>
       <c r="E17">
-        <v>-23.27472369701647</v>
+        <v>-26.50435437522884</v>
       </c>
       <c r="F17">
-        <v>0.1955508887965659</v>
+        <v>-0.1634229535740026</v>
       </c>
       <c r="G17">
-        <v>-1.854101974847016</v>
+        <v>-4.92732112549893</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-5.536092314627014</v>
       </c>
       <c r="E18">
-        <v>-23.94781343114655</v>
+        <v>-28.37991245498567</v>
       </c>
       <c r="F18">
-        <v>0.6710130688184122</v>
+        <v>0.04315779443834649</v>
       </c>
       <c r="G18">
-        <v>-1.177436398256603</v>
+        <v>-4.436449985663494</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-4.306077143009794</v>
       </c>
       <c r="E19">
-        <v>-24.28537041215231</v>
+        <v>-28.24062565145774</v>
       </c>
       <c r="F19">
-        <v>0.1093327527783878</v>
+        <v>-0.3074313130810855</v>
       </c>
       <c r="G19">
-        <v>-0.4217149941883941</v>
+        <v>-3.501426124642819</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-3.128639835006753</v>
       </c>
       <c r="E20">
-        <v>-26.69234038823525</v>
+        <v>-27.94099464026623</v>
       </c>
       <c r="F20">
-        <v>0.7244808711995091</v>
+        <v>0.4105544765605804</v>
       </c>
       <c r="G20">
-        <v>-0.2983971728505423</v>
+        <v>-3.323888188462784</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-2.037315485063216</v>
       </c>
       <c r="E21">
-        <v>-26.4112897058972</v>
+        <v>-28.72839664377194</v>
       </c>
       <c r="F21">
-        <v>0.9255687149638947</v>
+        <v>-0.02783743381858514</v>
       </c>
       <c r="G21">
-        <v>-0.1160523245474854</v>
+        <v>-2.980372741125848</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-1.052860751303359</v>
       </c>
       <c r="E22">
-        <v>-27.16104197650314</v>
+        <v>-29.24719673998668</v>
       </c>
       <c r="F22">
-        <v>1.168104750094756</v>
+        <v>0.5411581947555617</v>
       </c>
       <c r="G22">
-        <v>0.3233001056058117</v>
+        <v>-2.656005489188058</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-0.2058970971761298</v>
       </c>
       <c r="E23">
-        <v>-27.67350220910715</v>
+        <v>-30.660177992571</v>
       </c>
       <c r="F23">
-        <v>1.443126041293803</v>
+        <v>0.5110843161969256</v>
       </c>
       <c r="G23">
-        <v>0.2891253440039152</v>
+        <v>-2.419966902783561</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>0.4889034786692771</v>
       </c>
       <c r="E24">
-        <v>-28.24471486348667</v>
+        <v>-31.0663662614</v>
       </c>
       <c r="F24">
-        <v>1.671450605262237</v>
+        <v>0.2581439864869022</v>
       </c>
       <c r="G24">
-        <v>1.491187739858822</v>
+        <v>-2.945992725700517</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>1.029667133487549</v>
       </c>
       <c r="E25">
-        <v>-29.13956396977237</v>
+        <v>-31.91019757951529</v>
       </c>
       <c r="F25">
-        <v>1.61489961940792</v>
+        <v>0.5785556695223482</v>
       </c>
       <c r="G25">
-        <v>0.8719468861926077</v>
+        <v>-1.922722962785029</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>1.40913987733022</v>
       </c>
       <c r="E26">
-        <v>-29.45191093597743</v>
+        <v>-30.40686647776694</v>
       </c>
       <c r="F26">
-        <v>1.659979373468269</v>
+        <v>1.081590058546376</v>
       </c>
       <c r="G26">
-        <v>0.1506683979149764</v>
+        <v>-1.404546443341685</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>1.633094374816583</v>
       </c>
       <c r="E27">
-        <v>-29.84913509050825</v>
+        <v>-31.08676703680456</v>
       </c>
       <c r="F27">
-        <v>1.780765281205271</v>
+        <v>0.7135232271952772</v>
       </c>
       <c r="G27">
-        <v>0.8472336637419483</v>
+        <v>-2.531187990720916</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>1.715756126532059</v>
       </c>
       <c r="E28">
-        <v>-29.21572384563337</v>
+        <v>-31.00545149328583</v>
       </c>
       <c r="F28">
-        <v>2.04150717511486</v>
+        <v>0.9420929879149392</v>
       </c>
       <c r="G28">
-        <v>0.4733505821732782</v>
+        <v>-1.491838908121188</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>1.668819225038367</v>
       </c>
       <c r="E29">
-        <v>-29.92646331266323</v>
+        <v>-30.54400678461523</v>
       </c>
       <c r="F29">
-        <v>2.185285248483964</v>
+        <v>0.7803211178222237</v>
       </c>
       <c r="G29">
-        <v>1.351452923191725</v>
+        <v>-3.065364376755558</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>1.511997850360234</v>
       </c>
       <c r="E30">
-        <v>-29.67351860425379</v>
+        <v>-32.38488581042132</v>
       </c>
       <c r="F30">
-        <v>1.475864777787245</v>
+        <v>0.9041371935186658</v>
       </c>
       <c r="G30">
-        <v>0.3783875833792842</v>
+        <v>-3.415332077348533</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>1.266896969867501</v>
       </c>
       <c r="E31">
-        <v>-29.13030324042669</v>
+        <v>-31.99750655838318</v>
       </c>
       <c r="F31">
-        <v>1.941158747939728</v>
+        <v>0.873393165731165</v>
       </c>
       <c r="G31">
-        <v>0.8899860488360963</v>
+        <v>-2.538881698554182</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>0.9534525050483509</v>
       </c>
       <c r="E32">
-        <v>-27.55875520622679</v>
+        <v>-31.98409774684646</v>
       </c>
       <c r="F32">
-        <v>2.078124327788209</v>
+        <v>1.249087604127242</v>
       </c>
       <c r="G32">
-        <v>0.1249454590748392</v>
+        <v>-2.171421075331698</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>0.5945197239653643</v>
       </c>
       <c r="E33">
-        <v>-29.2071786151809</v>
+        <v>-30.69298678675657</v>
       </c>
       <c r="F33">
-        <v>1.798235549730312</v>
+        <v>0.9922605745632829</v>
       </c>
       <c r="G33">
-        <v>0.1977344238467948</v>
+        <v>-1.96577991806879</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>0.2074886529967511</v>
       </c>
       <c r="E34">
-        <v>-28.27597039108761</v>
+        <v>-30.41597776747037</v>
       </c>
       <c r="F34">
-        <v>1.83629903188895</v>
+        <v>0.8204356376701926</v>
       </c>
       <c r="G34">
-        <v>0.4311775425485025</v>
+        <v>-2.90164465765644</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-0.1924058138854695</v>
       </c>
       <c r="E35">
-        <v>-27.55794008090541</v>
+        <v>-30.0788826908134</v>
       </c>
       <c r="F35">
-        <v>1.632749280203444</v>
+        <v>0.7850726332446817</v>
       </c>
       <c r="G35">
-        <v>0.02473524560110039</v>
+        <v>-2.187507016107017</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-0.5904323050323692</v>
       </c>
       <c r="E36">
-        <v>-26.99911280293686</v>
+        <v>-29.99862454597546</v>
       </c>
       <c r="F36">
-        <v>1.671879699576887</v>
+        <v>0.9990167391005156</v>
       </c>
       <c r="G36">
-        <v>0.3668933692669347</v>
+        <v>-2.83755249601615</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-0.9801132857712467</v>
       </c>
       <c r="E37">
-        <v>-26.47930738549242</v>
+        <v>-28.49692822334387</v>
       </c>
       <c r="F37">
-        <v>1.916592684242306</v>
+        <v>0.5119764678897407</v>
       </c>
       <c r="G37">
-        <v>-0.0156865154334008</v>
+        <v>-3.083449887036596</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-1.355013299677705</v>
       </c>
       <c r="E38">
-        <v>-24.8939339201471</v>
+        <v>-29.18389320183346</v>
       </c>
       <c r="F38">
-        <v>2.052047321948081</v>
+        <v>0.44612125936718</v>
       </c>
       <c r="G38">
-        <v>-0.3923007970719696</v>
+        <v>-3.02033764687593</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-1.707039927681289</v>
       </c>
       <c r="E39">
-        <v>-25.39792590635676</v>
+        <v>-28.14966672253968</v>
       </c>
       <c r="F39">
-        <v>1.788528740504308</v>
+        <v>0.9362148928246738</v>
       </c>
       <c r="G39">
-        <v>-0.8956195881350645</v>
+        <v>-2.782196864053997</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-2.035500367162093</v>
       </c>
       <c r="E40">
-        <v>-25.31197094121717</v>
+        <v>-27.98262037334473</v>
       </c>
       <c r="F40">
-        <v>1.567205537824336</v>
+        <v>0.610642480869787</v>
       </c>
       <c r="G40">
-        <v>-0.4842247150609126</v>
+        <v>-2.803374423868714</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-2.337867046081205</v>
       </c>
       <c r="E41">
-        <v>-24.74000203167837</v>
+        <v>-28.71257415558913</v>
       </c>
       <c r="F41">
-        <v>1.966425610459918</v>
+        <v>0.363084054175752</v>
       </c>
       <c r="G41">
-        <v>-0.1264110215398649</v>
+        <v>-3.491547456753634</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-2.60778841568361</v>
       </c>
       <c r="E42">
-        <v>-23.15767622934021</v>
+        <v>-26.9413974017091</v>
       </c>
       <c r="F42">
-        <v>2.095526670186221</v>
+        <v>0.6080935943713729</v>
       </c>
       <c r="G42">
-        <v>-0.1775192235751335</v>
+        <v>-3.51841253380482</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-2.847538611136272</v>
       </c>
       <c r="E43">
-        <v>-21.67254053615468</v>
+        <v>-24.85626154487729</v>
       </c>
       <c r="F43">
-        <v>2.193050364517807</v>
+        <v>0.6181242952518722</v>
       </c>
       <c r="G43">
-        <v>-1.662451183033067</v>
+        <v>-3.255548596895609</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-3.059537911549299</v>
       </c>
       <c r="E44">
-        <v>-21.96994353813443</v>
+        <v>-24.57008462996256</v>
       </c>
       <c r="F44">
-        <v>1.010396850480175</v>
+        <v>0.6992852482759593</v>
       </c>
       <c r="G44">
-        <v>-0.8686055365346116</v>
+        <v>-2.447550368216769</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-3.244334527187201</v>
       </c>
       <c r="E45">
-        <v>-21.19826439638335</v>
+        <v>-24.76548828339354</v>
       </c>
       <c r="F45">
-        <v>1.904539938531573</v>
+        <v>0.841901950546339</v>
       </c>
       <c r="G45">
-        <v>-0.6033215908361936</v>
+        <v>-2.473610982701911</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-3.412888206964756</v>
       </c>
       <c r="E46">
-        <v>-20.93335319540864</v>
+        <v>-23.88093692700128</v>
       </c>
       <c r="F46">
-        <v>1.796431365527015</v>
+        <v>0.8117825117805489</v>
       </c>
       <c r="G46">
-        <v>-1.304475272780595</v>
+        <v>-2.416692773245222</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-3.576655340984189</v>
       </c>
       <c r="E47">
-        <v>-19.79964067064035</v>
+        <v>-22.9724661709005</v>
       </c>
       <c r="F47">
-        <v>1.825758885055729</v>
+        <v>0.9216488804138474</v>
       </c>
       <c r="G47">
-        <v>-0.6694530485286748</v>
+        <v>-3.296711920130907</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-3.742057786588642</v>
       </c>
       <c r="E48">
-        <v>-19.11369459880249</v>
+        <v>-22.23267201463744</v>
       </c>
       <c r="F48">
-        <v>1.98165597352779</v>
+        <v>1.301972235856768</v>
       </c>
       <c r="G48">
-        <v>-1.266377514714663</v>
+        <v>-3.827634039900445</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-3.922941634303559</v>
       </c>
       <c r="E49">
-        <v>-18.22202448127018</v>
+        <v>-21.69447646424784</v>
       </c>
       <c r="F49">
-        <v>1.95266974136903</v>
+        <v>1.128697656008778</v>
       </c>
       <c r="G49">
-        <v>-1.470946055222847</v>
+        <v>-2.914608753988226</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-4.132187209496677</v>
       </c>
       <c r="E50">
-        <v>-17.96010207314053</v>
+        <v>-20.84481247161067</v>
       </c>
       <c r="F50">
-        <v>1.970274205413325</v>
+        <v>0.5701891587540732</v>
       </c>
       <c r="G50">
-        <v>-1.352296103095368</v>
+        <v>-3.598365519123758</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-4.374810318847361</v>
       </c>
       <c r="E51">
-        <v>-17.7549803144891</v>
+        <v>-20.26168540211697</v>
       </c>
       <c r="F51">
-        <v>1.671175587284507</v>
+        <v>0.8535123480639768</v>
       </c>
       <c r="G51">
-        <v>-0.524000919715256</v>
+        <v>-3.00584738905054</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-4.660842659631099</v>
       </c>
       <c r="E52">
-        <v>-16.5945226222315</v>
+        <v>-20.11876223396088</v>
       </c>
       <c r="F52">
-        <v>2.203033848456347</v>
+        <v>0.6507868219442566</v>
       </c>
       <c r="G52">
-        <v>-1.615305704008306</v>
+        <v>-2.699165071383536</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-4.998411555416383</v>
       </c>
       <c r="E53">
-        <v>-16.68365204765047</v>
+        <v>-18.69979660297543</v>
       </c>
       <c r="F53">
-        <v>1.984848501498179</v>
+        <v>0.928451433525637</v>
       </c>
       <c r="G53">
-        <v>-1.446845283696953</v>
+        <v>-3.667069270700253</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-5.386292397012224</v>
       </c>
       <c r="E54">
-        <v>-15.6898150280311</v>
+        <v>-18.13748240002098</v>
       </c>
       <c r="F54">
-        <v>2.025345727086242</v>
+        <v>1.016735517846397</v>
       </c>
       <c r="G54">
-        <v>-2.204860895823876</v>
+        <v>-3.410369569585165</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-5.825685990211992</v>
       </c>
       <c r="E55">
-        <v>-14.10703637829218</v>
+        <v>-17.5320525960395</v>
       </c>
       <c r="F55">
-        <v>2.08002128914062</v>
+        <v>1.252916318262981</v>
       </c>
       <c r="G55">
-        <v>-1.733843097587451</v>
+        <v>-3.562058766194571</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-6.315115103348845</v>
       </c>
       <c r="E56">
-        <v>-13.67947144790997</v>
+        <v>-17.9828757689251</v>
       </c>
       <c r="F56">
-        <v>2.137619331392075</v>
+        <v>0.9193758402605655</v>
       </c>
       <c r="G56">
-        <v>-1.496662372971906</v>
+        <v>-4.105623859378586</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-6.842638128524997</v>
       </c>
       <c r="E57">
-        <v>-13.45330134207088</v>
+        <v>-17.01516804433</v>
       </c>
       <c r="F57">
-        <v>1.691286691089674</v>
+        <v>0.8141715233702227</v>
       </c>
       <c r="G57">
-        <v>-2.110255435948124</v>
+        <v>-4.649900719853544</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-7.395647763303986</v>
       </c>
       <c r="E58">
-        <v>-11.96059404034453</v>
+        <v>-17.10008146044782</v>
       </c>
       <c r="F58">
-        <v>1.899952439854869</v>
+        <v>0.6412390592595896</v>
       </c>
       <c r="G58">
-        <v>-2.843114212522126</v>
+        <v>-4.136209989615912</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-7.960347212866655</v>
       </c>
       <c r="E59">
-        <v>-12.18937707568604</v>
+        <v>-16.32525050078741</v>
       </c>
       <c r="F59">
-        <v>1.789819336917869</v>
+        <v>0.9736786369836843</v>
       </c>
       <c r="G59">
-        <v>-2.429173529928274</v>
+        <v>-5.034738396611662</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-8.516250730599241</v>
       </c>
       <c r="E60">
-        <v>-12.19234775463507</v>
+        <v>-14.94050201940391</v>
       </c>
       <c r="F60">
-        <v>1.618498047405681</v>
+        <v>0.3302483986961823</v>
       </c>
       <c r="G60">
-        <v>-3.578121533151115</v>
+        <v>-3.982607297684808</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-9.043948276674429</v>
       </c>
       <c r="E61">
-        <v>-11.63384652679508</v>
+        <v>-14.43711684871128</v>
       </c>
       <c r="F61">
-        <v>1.881251217369267</v>
+        <v>0.7727051079208851</v>
       </c>
       <c r="G61">
-        <v>-2.745833831850642</v>
+        <v>-5.313986223394726</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-9.526928316828238</v>
       </c>
       <c r="E62">
-        <v>-11.21014891321542</v>
+        <v>-15.37826054477739</v>
       </c>
       <c r="F62">
-        <v>1.480155720933747</v>
+        <v>0.1883598313728634</v>
       </c>
       <c r="G62">
-        <v>-2.975271190449832</v>
+        <v>-5.171010382644682</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-9.948273586559685</v>
       </c>
       <c r="E63">
-        <v>-9.820133816561002</v>
+        <v>-14.51737952202323</v>
       </c>
       <c r="F63">
-        <v>1.044374824608205</v>
+        <v>0.4455803354531519</v>
       </c>
       <c r="G63">
-        <v>-2.817301888952428</v>
+        <v>-4.450648915481429</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-10.29208802358799</v>
       </c>
       <c r="E64">
-        <v>-10.18488881245683</v>
+        <v>-14.43784593302651</v>
       </c>
       <c r="F64">
-        <v>1.08967823786731</v>
+        <v>0.4085183494844992</v>
       </c>
       <c r="G64">
-        <v>-3.289160565755829</v>
+        <v>-4.671306707310471</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-10.54757697775166</v>
       </c>
       <c r="E65">
-        <v>-9.616542682124159</v>
+        <v>-15.08061300520123</v>
       </c>
       <c r="F65">
-        <v>1.358579550694475</v>
+        <v>0.1116513531388236</v>
       </c>
       <c r="G65">
-        <v>-2.576062435505737</v>
+        <v>-5.278596491579917</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-10.70840549365981</v>
       </c>
       <c r="E66">
-        <v>-10.13700019982571</v>
+        <v>-14.11519668845401</v>
       </c>
       <c r="F66">
-        <v>0.7702730212262657</v>
+        <v>0.2527728522471502</v>
       </c>
       <c r="G66">
-        <v>-2.82992168854813</v>
+        <v>-5.334104408636877</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-10.76810493056391</v>
       </c>
       <c r="E67">
-        <v>-10.07485142254444</v>
+        <v>-13.19905922585825</v>
       </c>
       <c r="F67">
-        <v>0.7138164692558683</v>
+        <v>-0.110218572026996</v>
       </c>
       <c r="G67">
-        <v>-3.290216629782857</v>
+        <v>-4.939596628358547</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-10.72566323232178</v>
       </c>
       <c r="E68">
-        <v>-9.269770256512793</v>
+        <v>-13.80861446966072</v>
       </c>
       <c r="F68">
-        <v>0.3987543829077015</v>
+        <v>-0.2811869770255915</v>
       </c>
       <c r="G68">
-        <v>-3.04391204166108</v>
+        <v>-5.641101228130112</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-10.58792167578651</v>
       </c>
       <c r="E69">
-        <v>-8.58985611205315</v>
+        <v>-13.22062834755678</v>
       </c>
       <c r="F69">
-        <v>0.5983188590183388</v>
+        <v>-0.1030299997055019</v>
       </c>
       <c r="G69">
-        <v>-3.8460075676434</v>
+        <v>-4.713161934563477</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-10.35921621247465</v>
       </c>
       <c r="E70">
-        <v>-8.934735635529309</v>
+        <v>-14.65591459886588</v>
       </c>
       <c r="F70">
-        <v>0.1412406367668219</v>
+        <v>-0.1278164091320687</v>
       </c>
       <c r="G70">
-        <v>-2.776817227552681</v>
+        <v>-4.183828876652789</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-10.04620229500286</v>
       </c>
       <c r="E71">
-        <v>-9.203740577006952</v>
+        <v>-13.64816157862094</v>
       </c>
       <c r="F71">
-        <v>0.6059796007594286</v>
+        <v>-0.2919855744884859</v>
       </c>
       <c r="G71">
-        <v>-2.311887522562975</v>
+        <v>-3.968759285694036</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-9.664373004661588</v>
       </c>
       <c r="E72">
-        <v>-8.955426233270355</v>
+        <v>-13.25926075931622</v>
       </c>
       <c r="F72">
-        <v>0.08484289888202322</v>
+        <v>-0.5012833675820174</v>
       </c>
       <c r="G72">
-        <v>-2.289975021638539</v>
+        <v>-4.992082017338153</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-9.222936624089186</v>
       </c>
       <c r="E73">
-        <v>-10.15225662875755</v>
+        <v>-13.88697065541544</v>
       </c>
       <c r="F73">
-        <v>-0.2326065423210117</v>
+        <v>-0.2544572176720571</v>
       </c>
       <c r="G73">
-        <v>-1.656588206883018</v>
+        <v>-4.219218608467598</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-8.728874245487315</v>
       </c>
       <c r="E74">
-        <v>-9.199076248779051</v>
+        <v>-14.04123765096073</v>
       </c>
       <c r="F74">
-        <v>0.037941564902918</v>
+        <v>-0.7929142535745973</v>
       </c>
       <c r="G74">
-        <v>-1.426703924636027</v>
+        <v>-3.955219154438417</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-8.197744331435958</v>
       </c>
       <c r="E75">
-        <v>-9.83864168983035</v>
+        <v>-15.39790959349667</v>
       </c>
       <c r="F75">
-        <v>-0.3645124540731938</v>
+        <v>-1.145248731211728</v>
       </c>
       <c r="G75">
-        <v>-1.82814398727359</v>
+        <v>-3.539921148173464</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-7.637027824226649</v>
       </c>
       <c r="E76">
-        <v>-8.181265487763078</v>
+        <v>-15.03677737680699</v>
       </c>
       <c r="F76">
-        <v>-0.4187920565090342</v>
+        <v>-0.8808603639950152</v>
       </c>
       <c r="G76">
-        <v>-1.624297145692967</v>
+        <v>-3.664523461180553</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-7.049429371878264</v>
       </c>
       <c r="E77">
-        <v>-10.6792623198742</v>
+        <v>-15.57290341457508</v>
       </c>
       <c r="F77">
-        <v>-0.5144055356097643</v>
+        <v>-0.6579831440673914</v>
       </c>
       <c r="G77">
-        <v>-0.6039704577618907</v>
+        <v>-4.200278977437427</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-6.447845016520568</v>
       </c>
       <c r="E78">
-        <v>-10.32210157488924</v>
+        <v>-15.65477369615975</v>
       </c>
       <c r="F78">
-        <v>-0.7748533590913597</v>
+        <v>-1.044006495608975</v>
       </c>
       <c r="G78">
-        <v>-0.3477507857499972</v>
+        <v>-2.190380569635104</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-5.838987125869893</v>
       </c>
       <c r="E79">
-        <v>-10.02671827231692</v>
+        <v>-16.63187800432078</v>
       </c>
       <c r="F79">
-        <v>-0.8419047301435629</v>
+        <v>-1.119471594371413</v>
       </c>
       <c r="G79">
-        <v>-0.01660684709331819</v>
+        <v>-3.036784437115029</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-5.2241327711382</v>
       </c>
       <c r="E80">
-        <v>-11.32324755155699</v>
+        <v>-16.21039934300487</v>
       </c>
       <c r="F80">
-        <v>-0.6614921083856502</v>
+        <v>-0.5766358083776744</v>
       </c>
       <c r="G80">
-        <v>-0.1549611662705396</v>
+        <v>-2.548512075527922</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-4.614448113797075</v>
       </c>
       <c r="E81">
-        <v>-11.55895462365623</v>
+        <v>-16.10349112863179</v>
       </c>
       <c r="F81">
-        <v>-0.5662762456382638</v>
+        <v>-0.8967625330265574</v>
       </c>
       <c r="G81">
-        <v>1.278034954767308</v>
+        <v>-2.128615721508922</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-4.016493573484764</v>
       </c>
       <c r="E82">
-        <v>-12.54142517351634</v>
+        <v>-17.81375537863465</v>
       </c>
       <c r="F82">
-        <v>-0.6223774279928603</v>
+        <v>-1.286367745217846</v>
       </c>
       <c r="G82">
-        <v>1.303949905248723</v>
+        <v>-1.137517840144071</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-3.431885591469944</v>
       </c>
       <c r="E83">
-        <v>-13.0859741729387</v>
+        <v>-17.95836313912158</v>
       </c>
       <c r="F83">
-        <v>-0.4085832566369331</v>
+        <v>-1.239225356324526</v>
       </c>
       <c r="G83">
-        <v>1.371405581156912</v>
+        <v>-1.296311467480753</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-2.872523197911151</v>
       </c>
       <c r="E84">
-        <v>-14.59405111544709</v>
+        <v>-20.51634866641232</v>
       </c>
       <c r="F84">
-        <v>-0.4073075708366219</v>
+        <v>-1.475001913448544</v>
       </c>
       <c r="G84">
-        <v>1.959265773656376</v>
+        <v>-1.080904200876994</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-2.348557548746403</v>
       </c>
       <c r="E85">
-        <v>-15.33025872029609</v>
+        <v>-20.17827996784369</v>
       </c>
       <c r="F85">
-        <v>-0.7735337698187001</v>
+        <v>-1.225414814985053</v>
       </c>
       <c r="G85">
-        <v>2.305674637794634</v>
+        <v>-0.8598458330377</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-1.86690099764424</v>
       </c>
       <c r="E86">
-        <v>-17.55122162651397</v>
+        <v>-21.1098549983316</v>
       </c>
       <c r="F86">
-        <v>-1.032368761967045</v>
+        <v>-1.199294734039979</v>
       </c>
       <c r="G86">
-        <v>2.62838661696279</v>
+        <v>-0.7524252513794286</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-1.442017385883414</v>
       </c>
       <c r="E87">
-        <v>-18.35796927098044</v>
+        <v>-21.35278498647308</v>
       </c>
       <c r="F87">
-        <v>-0.9368753961397206</v>
+        <v>-1.508680018576761</v>
       </c>
       <c r="G87">
-        <v>2.683623069285529</v>
+        <v>-1.047461069839277</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-1.08568559318705</v>
       </c>
       <c r="E88">
-        <v>-19.5201206125169</v>
+        <v>-23.75419852494861</v>
       </c>
       <c r="F88">
-        <v>-0.7126156310168245</v>
+        <v>-1.736753587222146</v>
       </c>
       <c r="G88">
-        <v>3.164890316511539</v>
+        <v>0.5915569211984952</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-0.8071496176578363</v>
       </c>
       <c r="E89">
-        <v>-19.60645596947314</v>
+        <v>-25.64386280123933</v>
       </c>
       <c r="F89">
-        <v>-1.345710329219597</v>
+        <v>-1.577957212840286</v>
       </c>
       <c r="G89">
-        <v>2.602097574835437</v>
+        <v>0.2698116213278071</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-0.6189739753391326</v>
       </c>
       <c r="E90">
-        <v>-23.33981598240272</v>
+        <v>-25.41646547894416</v>
       </c>
       <c r="F90">
-        <v>-0.8048725654014109</v>
+        <v>-1.942822404179565</v>
       </c>
       <c r="G90">
-        <v>2.595704911399104</v>
+        <v>0.6202593510239764</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-0.5280409095380718</v>
       </c>
       <c r="E91">
-        <v>-24.32160273268768</v>
+        <v>-27.2874769707973</v>
       </c>
       <c r="F91">
-        <v>-1.145901484725134</v>
+        <v>-1.921979023590324</v>
       </c>
       <c r="G91">
-        <v>3.038735357646531</v>
+        <v>0.1207079607845721</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-0.5403032213462531</v>
       </c>
       <c r="E92">
-        <v>-25.856202947459</v>
+        <v>-29.24514534126121</v>
       </c>
       <c r="F92">
-        <v>-1.403215594321939</v>
+        <v>-2.48986795331433</v>
       </c>
       <c r="G92">
-        <v>3.758116903330161</v>
+        <v>-0.8949674106638281</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-0.6606655184714347</v>
       </c>
       <c r="E93">
-        <v>-27.50746570961591</v>
+        <v>-32.39662814352321</v>
       </c>
       <c r="F93">
-        <v>-1.222800487461817</v>
+        <v>-2.444441113312208</v>
       </c>
       <c r="G93">
-        <v>2.73290385018312</v>
+        <v>-0.0002560626748577951</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-0.8855280259615043</v>
       </c>
       <c r="E94">
-        <v>-30.3600284711056</v>
+        <v>-32.66537496198242</v>
       </c>
       <c r="F94">
-        <v>-1.531329240104105</v>
+        <v>-1.993574818214285</v>
       </c>
       <c r="G94">
-        <v>2.034554200310481</v>
+        <v>0.2254668638292696</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-1.209775976657338</v>
       </c>
       <c r="E95">
-        <v>-32.3488572712163</v>
+        <v>-34.75829300139641</v>
       </c>
       <c r="F95">
-        <v>-1.479127183114485</v>
+        <v>-1.867122877442135</v>
       </c>
       <c r="G95">
-        <v>1.499755431714456</v>
+        <v>-1.396227042401496</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-1.630689077027585</v>
       </c>
       <c r="E96">
-        <v>-34.08811281181626</v>
+        <v>-38.02519302069191</v>
       </c>
       <c r="F96">
-        <v>-1.586836483030894</v>
+        <v>-2.620407058851893</v>
       </c>
       <c r="G96">
-        <v>2.674247604318313</v>
+        <v>-0.7335054836224938</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-2.124487158899114</v>
       </c>
       <c r="E97">
-        <v>-36.43609262123828</v>
+        <v>-38.32299226414732</v>
       </c>
       <c r="F97">
-        <v>-1.639291192078367</v>
+        <v>-1.948122298822676</v>
       </c>
       <c r="G97">
-        <v>1.656685221912528</v>
+        <v>-1.787414345503937</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-2.693554015161221</v>
       </c>
       <c r="E98">
-        <v>-39.27641944595924</v>
+        <v>-40.4150770643439</v>
       </c>
       <c r="F98">
-        <v>-1.707484881779031</v>
+        <v>-2.777061275130113</v>
       </c>
       <c r="G98">
-        <v>1.047918934332568</v>
+        <v>-1.559728265495022</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-3.300255817232514</v>
       </c>
       <c r="E99">
-        <v>-41.36067677883357</v>
+        <v>-41.52145345576489</v>
       </c>
       <c r="F99">
-        <v>-1.719348759721925</v>
+        <v>-2.626695195806544</v>
       </c>
       <c r="G99">
-        <v>0.4048686371479144</v>
+        <v>-1.959933494646437</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-3.961892123938182</v>
       </c>
       <c r="E100">
-        <v>-42.59851250646022</v>
+        <v>-44.24577436183137</v>
       </c>
       <c r="F100">
-        <v>-1.731702202799874</v>
+        <v>-2.907771024352653</v>
       </c>
       <c r="G100">
-        <v>0.8472733902884195</v>
+        <v>-2.543483356853769</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.606602284772806</v>
       </c>
       <c r="E101">
-        <v>-44.37678311487327</v>
+        <v>-46.27824180171697</v>
       </c>
       <c r="F101">
-        <v>-1.734126005820465</v>
+        <v>-2.688230468323505</v>
       </c>
       <c r="G101">
-        <v>0.6806635649335185</v>
+        <v>-2.09142174237521</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-5.320307568699368</v>
       </c>
       <c r="E102">
-        <v>-46.92470410868195</v>
+        <v>-48.32904956133364</v>
       </c>
       <c r="F102">
-        <v>-1.804523152812576</v>
+        <v>-2.520134841477819</v>
       </c>
       <c r="G102">
-        <v>-0.7155093580710156</v>
+        <v>-1.61160782464094</v>
       </c>
     </row>
   </sheetData>
